--- a/data/trans_orig/P33B_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R3-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43308</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34441</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>55188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>295819</t>
+          <t>304719</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285531</t>
+          <t>296947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301543</t>
+          <t>310740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>261822</t>
+          <t>286879</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253847</t>
+          <t>278521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268591</t>
+          <t>293547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557639</t>
+          <t>591598</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545328</t>
+          <t>579718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566636</t>
+          <t>600947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55201</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74794</t>
+          <t>74053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63684</t>
+          <t>66662</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>96833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131684</t>
+          <t>137132</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112313</t>
+          <t>115498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158451</t>
+          <t>161747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>463189</t>
+          <t>474384</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443596</t>
+          <t>456594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479034</t>
+          <t>489976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>438486</t>
+          <t>465625</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424817</t>
+          <t>449661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451285</t>
+          <t>479832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>901675</t>
+          <t>940009</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>874908</t>
+          <t>915394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921046</t>
+          <t>961643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>50829</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38358</t>
+          <t>39379</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>64113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>75969</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61579</t>
+          <t>64085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86114</t>
+          <t>89116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123054</t>
+          <t>126798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107942</t>
+          <t>110490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141752</t>
+          <t>144227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>265162</t>
+          <t>264177</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252905</t>
+          <t>250893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276723</t>
+          <t>275627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>275992</t>
+          <t>280412</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>267265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287549</t>
+          <t>292296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>541155</t>
+          <t>544589</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>522457</t>
+          <t>527160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556267</t>
+          <t>560897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>315006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>315006</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>315006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664209</t>
+          <t>671387</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664209</t>
+          <t>671387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664209</t>
+          <t>671387</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56845</t>
+          <t>64861</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41822</t>
+          <t>47891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77865</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>90768</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>76258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105200</t>
+          <t>108245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>137703</t>
+          <t>155630</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96862</t>
+          <t>131462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>182303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>255712</t>
+          <t>308284</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234692</t>
+          <t>285607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270735</t>
+          <t>325254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>394859</t>
+          <t>331193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370518</t>
+          <t>313716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>425476</t>
+          <t>345703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>650571</t>
+          <t>639477</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>623856</t>
+          <t>612804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691412</t>
+          <t>663645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,67 +2097,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>25051</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19480</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32009</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>8,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>22894</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17748</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29545</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46944</t>
+          <t>49821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -2210,69 +2210,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163390</t>
+          <t>189357</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156643</t>
+          <t>182256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168302</t>
+          <t>194544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>201772</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>194814</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>207343</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>85,89%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>91,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>185380</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>178729</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>190526</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,01%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>682</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>348770</t>
+          <t>391129</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340072</t>
+          <t>382667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355782</t>
+          <t>399235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44954</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35551</t>
+          <t>35455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56534</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>65323</t>
+          <t>68142</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55443</t>
+          <t>57944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76604</t>
+          <t>79426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>110277</t>
+          <t>112636</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96838</t>
+          <t>98317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125320</t>
+          <t>127395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>224682</t>
+          <t>226213</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213102</t>
+          <t>215206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234085</t>
+          <t>235252</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>191733</t>
+          <t>195608</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180452</t>
+          <t>184324</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201613</t>
+          <t>205806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>416415</t>
+          <t>421821</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>401372</t>
+          <t>407062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>429854</t>
+          <t>436140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>112230</t>
+          <t>130608</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92390</t>
+          <t>110582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136813</t>
+          <t>155889</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>159693</t>
+          <t>194710</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>173130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217739</t>
+          <t>217353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>271923</t>
+          <t>325318</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180345</t>
+          <t>293976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325840</t>
+          <t>358319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>511020</t>
+          <t>587997</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>486437</t>
+          <t>562716</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>530860</t>
+          <t>608023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>689572</t>
+          <t>577347</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>631526</t>
+          <t>554704</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>768922</t>
+          <t>598927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1200591</t>
+          <t>1165344</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1146674</t>
+          <t>1132343</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292169</t>
+          <t>1196686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>150206</t>
+          <t>167946</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69175</t>
+          <t>145765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>212722</t>
+          <t>189021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>228297</t>
+          <t>257409</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>207218</t>
+          <t>234389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248924</t>
+          <t>277672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>378502</t>
+          <t>425355</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>229979</t>
+          <t>392089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>455639</t>
+          <t>460753</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>778514</t>
+          <t>630126</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>715998</t>
+          <t>609051</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>859545</t>
+          <t>652307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>487095</t>
+          <t>573200</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>466468</t>
+          <t>552937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>508174</t>
+          <t>596220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1265610</t>
+          <t>1203326</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1188473</t>
+          <t>1167928</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1414133</t>
+          <t>1236592</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>500330</t>
+          <t>545433</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>395284</t>
+          <t>502273</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>558367</t>
+          <t>593798</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>734497</t>
+          <t>822101</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>605619</t>
+          <t>778040</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>799633</t>
+          <t>864171</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1234827</t>
+          <t>1367535</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1074122</t>
+          <t>1309728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1331942</t>
+          <t>1428418</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2957488</t>
+          <t>2985259</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2899451</t>
+          <t>2936894</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3062534</t>
+          <t>3028419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2924938</t>
+          <t>2912036</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2859802</t>
+          <t>2869966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3053816</t>
+          <t>2956097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5882426</t>
+          <t>5897295</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5785311</t>
+          <t>5836412</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6043131</t>
+          <t>5955102</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
